--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30102/BU12/HRM/post FET_HRM-2031-0300/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU12_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.81961</v>
+        <v>17.93152</v>
       </c>
       <c r="D2" t="n">
-        <v>17.97078</v>
+        <v>17.61301</v>
       </c>
       <c r="E2" t="n">
-        <v>17.94311</v>
+        <v>17.71352</v>
       </c>
       <c r="F2" t="n">
-        <v>44.67598</v>
+        <v>45.0288</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05312</v>
+        <v>0.05371</v>
       </c>
       <c r="H2" t="n">
-        <v>1.89976</v>
+        <v>1.91442</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.67489</v>
+        <v>18.00938</v>
       </c>
       <c r="D3" t="n">
-        <v>17.45422</v>
+        <v>17.60325</v>
       </c>
       <c r="E3" t="n">
-        <v>17.48781</v>
+        <v>17.94604</v>
       </c>
       <c r="F3" t="n">
-        <v>45.46704</v>
+        <v>45.63108</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05363</v>
+        <v>0.05323</v>
       </c>
       <c r="H3" t="n">
-        <v>1.91512</v>
+        <v>1.92778</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.81466</v>
+        <v>17.9078</v>
       </c>
       <c r="D4" t="n">
-        <v>17.68379</v>
+        <v>17.45118</v>
       </c>
       <c r="E4" t="n">
-        <v>17.4536</v>
+        <v>17.45761</v>
       </c>
       <c r="F4" t="n">
-        <v>44.48148</v>
+        <v>44.28413</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0543</v>
+        <v>0.05161</v>
       </c>
       <c r="H4" t="n">
-        <v>1.90791</v>
+        <v>1.94029</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.6677</v>
+        <v>17.84741</v>
       </c>
       <c r="D6" t="n">
-        <v>17.39309</v>
+        <v>16.95881</v>
       </c>
       <c r="E6" t="n">
-        <v>17.25117</v>
+        <v>17.24332</v>
       </c>
       <c r="F6" t="n">
-        <v>22.69105</v>
+        <v>23.47371</v>
       </c>
       <c r="G6" t="n">
-        <v>35.64663</v>
+        <v>36.04855</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.51371</v>
+        <v>17.92594</v>
       </c>
       <c r="D7" t="n">
-        <v>16.54785</v>
+        <v>16.56565</v>
       </c>
       <c r="E7" t="n">
-        <v>17.42773</v>
+        <v>17.83366</v>
       </c>
       <c r="F7" t="n">
-        <v>23.07068</v>
+        <v>22.91313</v>
       </c>
       <c r="G7" t="n">
-        <v>36.15453</v>
+        <v>36.54021</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.80266</v>
+        <v>17.94638</v>
       </c>
       <c r="D8" t="n">
-        <v>16.76677</v>
+        <v>16.92523</v>
       </c>
       <c r="E8" t="n">
-        <v>17.0819</v>
+        <v>17.21829</v>
       </c>
       <c r="F8" t="n">
-        <v>22.76075</v>
+        <v>23.16525</v>
       </c>
       <c r="G8" t="n">
-        <v>36.56991</v>
+        <v>36.34557</v>
       </c>
     </row>
   </sheetData>
